--- a/docs/oc-regiones/mobiliario-general-escolar-y-clinico/los-rios.xlsx
+++ b/docs/oc-regiones/mobiliario-general-escolar-y-clinico/los-rios.xlsx
@@ -569,7 +569,7 @@
         </is>
       </c>
       <c r="M2" s="2" t="n">
-        <v>7257.54</v>
+        <v>7217.87</v>
       </c>
     </row>
     <row r="3">
@@ -630,7 +630,7 @@
         </is>
       </c>
       <c r="M3" s="2" t="n">
-        <v>38138.6</v>
+        <v>37929.74</v>
       </c>
     </row>
     <row r="4">
@@ -691,7 +691,7 @@
         </is>
       </c>
       <c r="M4" s="2" t="n">
-        <v>8619.01</v>
+        <v>8679.84</v>
       </c>
     </row>
     <row r="5">
@@ -752,7 +752,7 @@
         </is>
       </c>
       <c r="M5" s="2" t="n">
-        <v>13421.13</v>
+        <v>13513.51</v>
       </c>
     </row>
     <row r="6">
@@ -813,7 +813,7 @@
         </is>
       </c>
       <c r="M6" s="2" t="n">
-        <v>69235.67999999999</v>
+        <v>69978.34</v>
       </c>
     </row>
     <row r="7">
@@ -874,7 +874,7 @@
         </is>
       </c>
       <c r="M7" s="2" t="n">
-        <v>13861.28</v>
+        <v>13801.56</v>
       </c>
     </row>
     <row r="8">
@@ -935,7 +935,7 @@
         </is>
       </c>
       <c r="M8" s="2" t="n">
-        <v>12294.67</v>
+        <v>12071.71</v>
       </c>
     </row>
     <row r="9">
@@ -996,7 +996,7 @@
         </is>
       </c>
       <c r="M9" s="2" t="n">
-        <v>13485.71</v>
+        <v>13451.66</v>
       </c>
     </row>
   </sheetData>

--- a/docs/oc-regiones/mobiliario-general-escolar-y-clinico/los-rios.xlsx
+++ b/docs/oc-regiones/mobiliario-general-escolar-y-clinico/los-rios.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M9"/>
+  <dimension ref="A1:M10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -514,7 +514,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>5737-101-CM25</t>
+          <t>696750-48-CM25</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -524,12 +524,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>nov-2025</t>
+          <t>oct-2025</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2025-11-07</t>
+          <t>2025-10-30</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -539,12 +539,12 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>60.908.000-0</t>
+          <t>61.935.400-1</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>JUNTA NACIONAL DE AUXILIO ESCOLAR Y BECA</t>
+          <t>MINISTERIO PUBLICO</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -554,12 +554,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>EVENTAIL SPA</t>
+          <t>MELMAN SPA</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>76.710.414-6</t>
+          <t>96.882.140-7</t>
         </is>
       </c>
       <c r="K2" t="inlineStr"/>
@@ -569,13 +569,13 @@
         </is>
       </c>
       <c r="M2" s="2" t="n">
-        <v>7217.87</v>
+        <v>9042.18</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>1079694-418-CM25</t>
+          <t>5737-101-CM25</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -590,22 +590,22 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>2025-11-07</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>60.505.523-0</t>
+          <t>60.908.000-0</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS XIV ZONA</t>
+          <t>JUNTA NACIONAL DE AUXILIO ESCOLAR Y BECA</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -615,12 +615,12 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>JOSÉ HERNÁN HENRÍQUEZ SEPÚLVEDA</t>
+          <t>EVENTAIL SPA</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>11.372.911-2</t>
+          <t>76.710.414-6</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
@@ -630,13 +630,13 @@
         </is>
       </c>
       <c r="M3" s="2" t="n">
-        <v>37929.74</v>
+        <v>7217.87</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>5740-485-CM25</t>
+          <t>1079694-418-CM25</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -651,7 +651,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2025-11-28</t>
+          <t>2025-11-11</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -661,12 +661,12 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>61.979.060-k</t>
+          <t>60.505.523-0</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>DIRECCION REGIONAL DE GENDARMERIA DE CHILE, REGION</t>
+          <t>SECCIÓN COMPRAS XIV ZONA</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -676,12 +676,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>EVENTAIL SPA</t>
+          <t>JOSÉ HERNÁN HENRÍQUEZ SEPÚLVEDA</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>76.710.414-6</t>
+          <t>11.372.911-2</t>
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
@@ -691,13 +691,13 @@
         </is>
       </c>
       <c r="M4" s="2" t="n">
-        <v>8679.84</v>
+        <v>37929.74</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>1495209-4-CM25</t>
+          <t>5740-485-CM25</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -707,12 +707,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>dic-2025</t>
+          <t>nov-2025</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2025-12-22</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -722,12 +722,12 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>61.981.340-5</t>
+          <t>61.979.060-k</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Servicio de Biodiversidad y Áreas Protegidas</t>
+          <t>DIRECCION REGIONAL DE GENDARMERIA DE CHILE, REGION</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -737,12 +737,12 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>MELMAN SPA</t>
+          <t>EVENTAIL SPA</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>96.882.140-7</t>
+          <t>76.710.414-6</t>
         </is>
       </c>
       <c r="K5" t="inlineStr"/>
@@ -752,13 +752,13 @@
         </is>
       </c>
       <c r="M5" s="2" t="n">
-        <v>13513.51</v>
+        <v>8679.84</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>3762-3515-CM25</t>
+          <t>1495209-4-CM25</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -773,22 +773,22 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2025-12-24</t>
+          <t>2025-12-22</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>69.200.900-2</t>
+          <t>61.981.340-5</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PAILLACO</t>
+          <t>Servicio de Biodiversidad y Áreas Protegidas</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -798,12 +798,12 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>COMERCIAL INNOVA PLACE SPA</t>
+          <t>MELMAN SPA</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>77.599.784-2</t>
+          <t>96.882.140-7</t>
         </is>
       </c>
       <c r="K6" t="inlineStr"/>
@@ -813,13 +813,13 @@
         </is>
       </c>
       <c r="M6" s="2" t="n">
-        <v>69978.34</v>
+        <v>13513.51</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>1432083-499-CM26</t>
+          <t>3762-3515-CM25</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -829,27 +829,27 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>dic-2025</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2025-12-24</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>61.981.110-0</t>
+          <t>69.200.900-2</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Servicio local de educación pública de Valdivia</t>
+          <t>I MUNICIPALIDAD DE PAILLACO</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -859,12 +859,12 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>ENILDA TERESA FIGUEROA MELLADO</t>
+          <t>COMERCIAL INNOVA PLACE SPA</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>6.189.318-0</t>
+          <t>77.599.784-2</t>
         </is>
       </c>
       <c r="K7" t="inlineStr"/>
@@ -874,13 +874,13 @@
         </is>
       </c>
       <c r="M7" s="2" t="n">
-        <v>13801.56</v>
+        <v>69978.34</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>5418-65-CM26</t>
+          <t>1432083-499-CM26</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -890,12 +890,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>mar-2026</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -905,12 +905,12 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>61.978.900-8</t>
+          <t>61.981.110-0</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>GOBIERNO REGIONAL DE LOS RIOS</t>
+          <t>Servicio local de educación pública de Valdivia</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -920,12 +920,12 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>STATUS SPA</t>
+          <t>ENILDA TERESA FIGUEROA MELLADO</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>77.393.671-4</t>
+          <t>6.189.318-0</t>
         </is>
       </c>
       <c r="K8" t="inlineStr"/>
@@ -935,13 +935,13 @@
         </is>
       </c>
       <c r="M8" s="2" t="n">
-        <v>12071.71</v>
+        <v>13801.56</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>1432083-1012-CM26</t>
+          <t>5418-65-CM26</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -951,12 +951,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>abr-2026</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -966,12 +966,12 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>61.981.110-0</t>
+          <t>61.978.900-8</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Servicio local de educación pública de Valdivia</t>
+          <t>GOBIERNO REGIONAL DE LOS RIOS</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -981,12 +981,12 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>MELMAN SPA</t>
+          <t>STATUS SPA</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>96.882.140-7</t>
+          <t>77.393.671-4</t>
         </is>
       </c>
       <c r="K9" t="inlineStr"/>
@@ -996,6 +996,67 @@
         </is>
       </c>
       <c r="M9" s="2" t="n">
+        <v>12071.71</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>1432083-1012-CM26</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>2239-4-LR25</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>may-2026</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>61.981.110-0</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Servicio local de educación pública de Valdivia</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Los Ríos</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>MELMAN SPA</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>96.882.140-7</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="n">
         <v>13451.66</v>
       </c>
     </row>

--- a/docs/oc-regiones/mobiliario-general-escolar-y-clinico/los-rios.xlsx
+++ b/docs/oc-regiones/mobiliario-general-escolar-y-clinico/los-rios.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Los Ríos" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Los Ríos" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M10"/>
+  <dimension ref="A1:M18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -514,37 +514,37 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>696750-48-CM25</t>
+          <t>5751-29-CM25</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2239-4-LR25</t>
+          <t>2239-3-LR23</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>oct-2025</t>
+          <t>ene-2025</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2025-10-30</t>
+          <t>2025-01-31</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>61.935.400-1</t>
+          <t>61.818.002-6</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>MINISTERIO PUBLICO</t>
+          <t>SERVICIO DE VIVIENDA Y URBANIZACION DE V</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -554,12 +554,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>MELMAN SPA</t>
+          <t>COMERCIALIZADORA MERCADO PUBLICO SPA</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>96.882.140-7</t>
+          <t>76.559.762-5</t>
         </is>
       </c>
       <c r="K2" t="inlineStr"/>
@@ -569,43 +569,43 @@
         </is>
       </c>
       <c r="M2" s="2" t="n">
-        <v>9042.18</v>
+        <v>5636.27</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>5737-101-CM25</t>
+          <t>1057935-3-CM25</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2239-4-LR25</t>
+          <t>2239-3-LR23</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>nov-2025</t>
+          <t>feb-2025</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2025-11-07</t>
+          <t>2025-02-21</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>60.908.000-0</t>
+          <t>61.607.500-4</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>JUNTA NACIONAL DE AUXILIO ESCOLAR Y BECA</t>
+          <t>SERVICIO DE SALUD LOS RIOS</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -615,12 +615,12 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>EVENTAIL SPA</t>
+          <t>IMPORTADORA Y DISTRIBUIDORA ARQUIMED LTDA</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>76.710.414-6</t>
+          <t>92.999.000-5</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
@@ -630,43 +630,43 @@
         </is>
       </c>
       <c r="M3" s="2" t="n">
-        <v>7217.87</v>
+        <v>37900.62</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>1079694-418-CM25</t>
+          <t>3143-74-CM25</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2239-4-LR25</t>
+          <t>2239-3-LR23</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>nov-2025</t>
+          <t>may-2025</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>2025-05-20</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>60.505.523-0</t>
+          <t>69.201.100-7</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS XIV ZONA</t>
+          <t>I MUNICIPALIDAD DE LAGO RANCO</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -676,12 +676,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>JOSÉ HERNÁN HENRÍQUEZ SEPÚLVEDA</t>
+          <t>EVENTAIL SPA</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>11.372.911-2</t>
+          <t>76.710.414-6</t>
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
@@ -691,28 +691,28 @@
         </is>
       </c>
       <c r="M4" s="2" t="n">
-        <v>37929.74</v>
+        <v>6238.56</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>5740-485-CM25</t>
+          <t>4230-64-CM25</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2239-4-LR25</t>
+          <t>2239-3-LR23</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>nov-2025</t>
+          <t>may-2025</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2025-11-28</t>
+          <t>2025-05-23</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -722,12 +722,12 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>61.979.060-k</t>
+          <t>60.505.523-0</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>DIRECCION REGIONAL DE GENDARMERIA DE CHILE, REGION</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -737,12 +737,12 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>EVENTAIL SPA</t>
+          <t>COMERCIAL LLICANCO SPA</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>76.710.414-6</t>
+          <t>76.956.267-2</t>
         </is>
       </c>
       <c r="K5" t="inlineStr"/>
@@ -752,28 +752,28 @@
         </is>
       </c>
       <c r="M5" s="2" t="n">
-        <v>8679.84</v>
+        <v>44540.99</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>1495209-4-CM25</t>
+          <t>5418-177-CM25</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2239-4-LR25</t>
+          <t>2239-3-LR23</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>dic-2025</t>
+          <t>jul-2025</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2025-12-22</t>
+          <t>2025-07-28</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>61.981.340-5</t>
+          <t>61.978.900-8</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Servicio de Biodiversidad y Áreas Protegidas</t>
+          <t>GOBIERNO REGIONAL DE LOS RIOS</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -798,12 +798,12 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>MELMAN SPA</t>
+          <t>EVENTAIL SPA</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>96.882.140-7</t>
+          <t>76.710.414-6</t>
         </is>
       </c>
       <c r="K6" t="inlineStr"/>
@@ -813,43 +813,43 @@
         </is>
       </c>
       <c r="M6" s="2" t="n">
-        <v>13513.51</v>
+        <v>6925.37</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>3762-3515-CM25</t>
+          <t>1057941-2-CM25</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2239-4-LR25</t>
+          <t>2239-3-LR23</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>dic-2025</t>
+          <t>jul-2025</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2025-12-24</t>
+          <t>2025-07-28</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>69.200.900-2</t>
+          <t>61.607.507-1</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PAILLACO</t>
+          <t>SERVICIO DE SALUD VALDIVIA HOSPITAL DE P</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -859,12 +859,12 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>COMERCIAL INNOVA PLACE SPA</t>
+          <t>IMPORTADORA Y DISTRIBUIDORA ARQUIMED LTDA</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>77.599.784-2</t>
+          <t>92.999.000-5</t>
         </is>
       </c>
       <c r="K7" t="inlineStr"/>
@@ -874,28 +874,28 @@
         </is>
       </c>
       <c r="M7" s="2" t="n">
-        <v>69978.34</v>
+        <v>9243.49</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>1432083-499-CM26</t>
+          <t>1035685-256-CM25</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2239-4-LR25</t>
+          <t>2239-3-LR23</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>sep-2025</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2025-09-01</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -905,12 +905,12 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>61.981.110-0</t>
+          <t>62.000.400-6</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Servicio local de educación pública de Valdivia</t>
+          <t>CENTRO DE FORMACION TECNICA ESTATAL DE LA REGION DE LOS RIOS</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -920,12 +920,12 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>ENILDA TERESA FIGUEROA MELLADO</t>
+          <t>MELMAN SPA</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>6.189.318-0</t>
+          <t>96.882.140-7</t>
         </is>
       </c>
       <c r="K8" t="inlineStr"/>
@@ -935,28 +935,28 @@
         </is>
       </c>
       <c r="M8" s="2" t="n">
-        <v>13801.56</v>
+        <v>14006.8</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>5418-65-CM26</t>
+          <t>5418-245-CM25</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2239-4-LR25</t>
+          <t>2239-3-LR23</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>oct-2025</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2025-10-06</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -981,12 +981,12 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>STATUS SPA</t>
+          <t>COMERCIAL E INDUSTRIAL MUEBLES ASENJO LIMITADA</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>77.393.671-4</t>
+          <t>77.018.060-0</t>
         </is>
       </c>
       <c r="K9" t="inlineStr"/>
@@ -996,13 +996,13 @@
         </is>
       </c>
       <c r="M9" s="2" t="n">
-        <v>12071.71</v>
+        <v>12193.41</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>1432083-1012-CM26</t>
+          <t>696750-48-CM25</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1012,27 +1012,27 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>oct-2025</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2025-10-30</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>61.981.110-0</t>
+          <t>61.935.400-1</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Servicio local de educación pública de Valdivia</t>
+          <t>MINISTERIO PUBLICO</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1057,6 +1057,494 @@
         </is>
       </c>
       <c r="M10" s="2" t="n">
+        <v>9042.18</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>5737-101-CM25</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>2239-4-LR25</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>nov-2025</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>2025-11-07</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>60.908.000-0</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>JUNTA NACIONAL DE AUXILIO ESCOLAR Y BECA</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Los Ríos</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>EVENTAIL SPA</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>76.710.414-6</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="n">
+        <v>7217.87</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>1079694-418-CM25</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>2239-4-LR25</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>nov-2025</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>2025-11-11</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>60.505.523-0</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>SECCIÓN COMPRAS XIV ZONA</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Los Ríos</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>JOSÉ HERNÁN HENRÍQUEZ SEPÚLVEDA</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>11.372.911-2</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="n">
+        <v>37929.74</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>5740-485-CM25</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>2239-4-LR25</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>nov-2025</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>2025-11-28</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>61.979.060-k</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>DIRECCION REGIONAL DE GENDARMERIA DE CHILE, REGION</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Los Ríos</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>EVENTAIL SPA</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>76.710.414-6</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="n">
+        <v>8679.84</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>1495209-4-CM25</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>2239-4-LR25</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>dic-2025</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>2025-12-22</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>61.981.340-5</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Servicio de Biodiversidad y Áreas Protegidas</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Los Ríos</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>MELMAN SPA</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>96.882.140-7</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="n">
+        <v>13513.51</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>3762-3515-CM25</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>2239-4-LR25</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>dic-2025</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>2025-12-24</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>69.200.900-2</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE PAILLACO</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Los Ríos</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>COMERCIAL INNOVA PLACE SPA</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>77.599.784-2</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="n">
+        <v>69978.34</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>1432083-499-CM26</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>2239-4-LR25</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>mar-2026</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>2026-03-26</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>61.981.110-0</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Servicio local de educación pública de Valdivia</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Los Ríos</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>ENILDA TERESA FIGUEROA MELLADO</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>6.189.318-0</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="n">
+        <v>13801.56</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>5418-65-CM26</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>2239-4-LR25</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>abr-2026</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>2026-04-07</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>61.978.900-8</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>GOBIERNO REGIONAL DE LOS RIOS</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Los Ríos</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>STATUS SPA</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>77.393.671-4</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="n">
+        <v>12071.71</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>1432083-1012-CM26</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>2239-4-LR25</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>may-2026</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>61.981.110-0</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Servicio local de educación pública de Valdivia</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>Los Ríos</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>MELMAN SPA</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>96.882.140-7</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="n">
         <v>13451.66</v>
       </c>
     </row>

--- a/docs/oc-regiones/mobiliario-general-escolar-y-clinico/los-rios.xlsx
+++ b/docs/oc-regiones/mobiliario-general-escolar-y-clinico/los-rios.xlsx
@@ -1154,7 +1154,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS XIV ZONA</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1215,7 +1215,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>DIRECCION REGIONAL DE GENDARMERIA DE CHILE, REGION</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1276,7 +1276,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Servicio de Biodiversidad y Áreas Protegidas</t>
+          <t>SERVICIO DE BIODIVERSIDAD Y ÁREAS PROTEGIDAS</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1398,7 +1398,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Servicio local de educación pública de Valdivia</t>
+          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA DE VALDIVIA</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -1520,7 +1520,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Servicio local de educación pública de Valdivia</t>
+          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA DE VALDIVIA</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">

--- a/docs/oc-regiones/mobiliario-general-escolar-y-clinico/los-rios.xlsx
+++ b/docs/oc-regiones/mobiliario-general-escolar-y-clinico/los-rios.xlsx
@@ -562,7 +562,11 @@
           <t>76.559.762-5</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr"/>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L2" t="inlineStr">
         <is>
           <t>USD</t>
@@ -684,7 +688,11 @@
           <t>76.710.414-6</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr"/>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L4" t="inlineStr">
         <is>
           <t>USD</t>
@@ -806,7 +814,11 @@
           <t>76.710.414-6</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr"/>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L6" t="inlineStr">
         <is>
           <t>USD</t>
@@ -928,7 +940,11 @@
           <t>96.882.140-7</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr"/>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L8" t="inlineStr">
         <is>
           <t>USD</t>
@@ -989,7 +1005,11 @@
           <t>77.018.060-0</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr"/>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L9" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1050,7 +1070,11 @@
           <t>96.882.140-7</t>
         </is>
       </c>
-      <c r="K10" t="inlineStr"/>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L10" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1111,7 +1135,11 @@
           <t>76.710.414-6</t>
         </is>
       </c>
-      <c r="K11" t="inlineStr"/>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L11" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1233,7 +1261,11 @@
           <t>76.710.414-6</t>
         </is>
       </c>
-      <c r="K13" t="inlineStr"/>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L13" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1294,7 +1326,11 @@
           <t>96.882.140-7</t>
         </is>
       </c>
-      <c r="K14" t="inlineStr"/>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L14" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1355,7 +1391,11 @@
           <t>77.599.784-2</t>
         </is>
       </c>
-      <c r="K15" t="inlineStr"/>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L15" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1477,7 +1517,11 @@
           <t>77.393.671-4</t>
         </is>
       </c>
-      <c r="K17" t="inlineStr"/>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L17" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1538,7 +1582,11 @@
           <t>96.882.140-7</t>
         </is>
       </c>
-      <c r="K18" t="inlineStr"/>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L18" t="inlineStr">
         <is>
           <t>USD</t>
